--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -434,12 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.03071</v>
+        <v>16.6222</v>
       </c>
       <c r="D2" t="n">
-        <v>16.14843</v>
+        <v>16.98538</v>
       </c>
       <c r="E2" t="n">
-        <v>16.39247</v>
+        <v>16.68461</v>
       </c>
       <c r="F2" t="n">
-        <v>22.14565</v>
+        <v>43.48564</v>
       </c>
       <c r="G2" t="n">
-        <v>34.12304</v>
+        <v>0.0511</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.80311</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.77645</v>
+        <v>16.95235</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94749</v>
+        <v>16.65209</v>
       </c>
       <c r="E3" t="n">
-        <v>16.34979</v>
+        <v>16.71443</v>
       </c>
       <c r="F3" t="n">
-        <v>22.13018</v>
+        <v>4249.133</v>
       </c>
       <c r="G3" t="n">
-        <v>34.58469</v>
+        <v>0.05114</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.81474</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.78634</v>
+        <v>17.04283</v>
       </c>
       <c r="D4" t="n">
-        <v>15.91702</v>
+        <v>16.92451</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77303</v>
+        <v>16.95469</v>
       </c>
       <c r="F4" t="n">
-        <v>21.9719</v>
+        <v>43.1617</v>
       </c>
       <c r="G4" t="n">
-        <v>33.85838</v>
+        <v>0.05128</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.85023</v>
+        <v>16.94134</v>
       </c>
       <c r="D5" t="n">
-        <v>16.04286</v>
+        <v>16.5145</v>
       </c>
       <c r="E5" t="n">
-        <v>16.41053</v>
+        <v>16.5978</v>
       </c>
       <c r="F5" t="n">
-        <v>21.75152</v>
+        <v>42.88985</v>
       </c>
       <c r="G5" t="n">
-        <v>34.57144</v>
+        <v>0.04968</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.8121</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.63515</v>
+        <v>17.38303</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10887</v>
+        <v>16.69151</v>
       </c>
       <c r="E6" t="n">
-        <v>16.83499</v>
+        <v>16.95522</v>
       </c>
       <c r="F6" t="n">
-        <v>22.09248</v>
+        <v>42.18217</v>
       </c>
       <c r="G6" t="n">
-        <v>34.73489</v>
+        <v>0.05132</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.86485</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.92075</v>
+        <v>16.92597</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9595</v>
+        <v>16.66064</v>
       </c>
       <c r="E7" t="n">
-        <v>16.11656</v>
+        <v>16.78754</v>
       </c>
       <c r="F7" t="n">
-        <v>22.20968</v>
+        <v>42.29543</v>
       </c>
       <c r="G7" t="n">
-        <v>34.00033</v>
+        <v>0.05196</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.85969</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.84959</v>
+        <v>16.94089</v>
       </c>
       <c r="D8" t="n">
-        <v>15.69974</v>
+        <v>16.601</v>
       </c>
       <c r="E8" t="n">
-        <v>16.30893</v>
+        <v>16.79828</v>
       </c>
       <c r="F8" t="n">
-        <v>22.51417</v>
+        <v>43.62091</v>
       </c>
       <c r="G8" t="n">
-        <v>34.9443</v>
+        <v>0.05163</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.80993</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.69151</v>
+        <v>16.87901</v>
       </c>
       <c r="D9" t="n">
-        <v>15.86853</v>
+        <v>16.50215</v>
       </c>
       <c r="E9" t="n">
-        <v>16.62615</v>
+        <v>16.6152</v>
       </c>
       <c r="F9" t="n">
-        <v>22.27456</v>
+        <v>43.18124</v>
       </c>
       <c r="G9" t="n">
-        <v>33.92347</v>
+        <v>0.05191</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.84513</v>
       </c>
     </row>
     <row r="10">
@@ -631,48 +660,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.02918</v>
+        <v>17.09249</v>
       </c>
       <c r="D10" t="n">
-        <v>16.07534</v>
+        <v>16.56982</v>
       </c>
       <c r="E10" t="n">
-        <v>16.31395</v>
+        <v>16.81436</v>
       </c>
       <c r="F10" t="n">
-        <v>22.34418</v>
+        <v>43.222</v>
       </c>
       <c r="G10" t="n">
-        <v>34.92081</v>
+        <v>0.05151</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.81215</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -686,26 +698,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.79828</v>
+        <v>0.61186</v>
       </c>
       <c r="D12" t="n">
-        <v>16.601</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.94089</v>
-      </c>
-      <c r="F12" t="n">
-        <v>43.62091</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05163</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.80993</v>
+        <v>1.12713</v>
       </c>
     </row>
     <row r="13">
@@ -715,22 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.50215</v>
+        <v>0.6089599999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>16.6152</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.87901</v>
-      </c>
-      <c r="F13" t="n">
-        <v>43.18124</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05191</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.84513</v>
+        <v>1.12029</v>
       </c>
     </row>
     <row r="14">
@@ -740,22 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.81436</v>
+        <v>0.60545</v>
       </c>
       <c r="D14" t="n">
-        <v>16.56982</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.09249</v>
-      </c>
-      <c r="F14" t="n">
-        <v>43.222</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05151</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.81215</v>
+        <v>1.12936</v>
       </c>
     </row>
     <row r="15">
@@ -765,22 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.92819</v>
+        <v>0.60848</v>
       </c>
       <c r="D15" t="n">
-        <v>16.80454</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.74649</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.7749</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05045</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.84804</v>
+        <v>1.14409</v>
       </c>
     </row>
     <row r="16">
@@ -790,22 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.83466</v>
+        <v>0.61688</v>
       </c>
       <c r="D16" t="n">
-        <v>17.05741</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.96428</v>
-      </c>
-      <c r="F16" t="n">
-        <v>43.32403</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05267</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.85983</v>
+        <v>1.13468</v>
       </c>
     </row>
     <row r="17">
@@ -815,22 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.95786</v>
+        <v>0.63201</v>
       </c>
       <c r="D17" t="n">
-        <v>16.64788</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.64508</v>
-      </c>
-      <c r="F17" t="n">
-        <v>43.00168</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05062</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.82903</v>
+        <v>1.13656</v>
       </c>
     </row>
     <row r="18">
@@ -840,22 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.5894</v>
+        <v>0.61293</v>
       </c>
       <c r="D18" t="n">
-        <v>16.85388</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.75407</v>
-      </c>
-      <c r="F18" t="n">
-        <v>43.08313</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05043</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.85039</v>
+        <v>1.11663</v>
       </c>
     </row>
     <row r="19">
@@ -865,22 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.32185</v>
+        <v>0.60528</v>
       </c>
       <c r="D19" t="n">
-        <v>16.53624</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.02547</v>
-      </c>
-      <c r="F19" t="n">
-        <v>42.91164</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05158</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.83563</v>
+        <v>1.12623</v>
       </c>
     </row>
     <row r="20">
@@ -890,22 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.79737</v>
+        <v>0.60739</v>
       </c>
       <c r="D20" t="n">
-        <v>16.52789</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.8824</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.64405</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05027</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.82664</v>
+        <v>1.11774</v>
       </c>
     </row>
     <row r="21">
@@ -962,28 +866,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.73809</v>
+        <v>0.73953</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08219</v>
+        <v>0.08221000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.59885</v>
+        <v>0.60924</v>
       </c>
       <c r="F22" t="n">
-        <v>0.98739</v>
+        <v>0.9745</v>
       </c>
       <c r="G22" t="n">
-        <v>0.10948</v>
+        <v>0.10893</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00768</v>
+        <v>0.00771</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09582</v>
+        <v>0.096</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12716</v>
+        <v>0.12604</v>
       </c>
     </row>
     <row r="23">
@@ -993,28 +897,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.74095</v>
+        <v>0.76357</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08075</v>
+        <v>0.08173999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.59806</v>
+        <v>0.619</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9724</v>
+        <v>0.9688</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11129</v>
+        <v>0.10928</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00767</v>
+        <v>0.00756</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09267</v>
+        <v>0.09413000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1279</v>
+        <v>0.12692</v>
       </c>
     </row>
     <row r="24">
@@ -1024,28 +928,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75001</v>
+        <v>0.74403</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.08118</v>
       </c>
       <c r="E24" t="n">
-        <v>0.61415</v>
+        <v>0.59845</v>
       </c>
       <c r="F24" t="n">
-        <v>0.97553</v>
+        <v>0.97602</v>
       </c>
       <c r="G24" t="n">
-        <v>0.11091</v>
+        <v>0.10779</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00778</v>
+        <v>0.0078</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09384000000000001</v>
+        <v>0.09326</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12726</v>
+        <v>0.12803</v>
       </c>
     </row>
     <row r="25">
@@ -1055,28 +959,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75173</v>
+        <v>0.77074</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0796</v>
+        <v>0.08137999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.61577</v>
+        <v>0.60077</v>
       </c>
       <c r="F25" t="n">
-        <v>0.97295</v>
+        <v>0.95885</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10723</v>
+        <v>0.10765</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00749</v>
+        <v>0.00768</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0944</v>
+        <v>0.0948</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12606</v>
+        <v>0.1279</v>
       </c>
     </row>
     <row r="26">
@@ -1086,28 +990,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7500599999999999</v>
+        <v>0.74541</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08107</v>
+        <v>0.08185000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6140600000000001</v>
+        <v>0.60812</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9805700000000001</v>
+        <v>0.96421</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10817</v>
+        <v>0.11055</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00756</v>
+        <v>0.0077</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09412</v>
+        <v>0.09447999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12573</v>
+        <v>0.12965</v>
       </c>
     </row>
     <row r="27">
@@ -1117,28 +1021,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.75483</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07897999999999999</v>
+        <v>0.08144999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60026</v>
+        <v>0.60951</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95399</v>
+        <v>0.9453</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1085</v>
+        <v>0.11084</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00761</v>
+        <v>0.00768</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09263</v>
+        <v>0.09135</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12789</v>
+        <v>0.12486</v>
       </c>
     </row>
     <row r="28">
@@ -1148,28 +1052,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75104</v>
+        <v>0.75934</v>
       </c>
       <c r="D28" t="n">
-        <v>0.07902000000000001</v>
+        <v>0.08068</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61327</v>
+        <v>0.60816</v>
       </c>
       <c r="F28" t="n">
-        <v>0.95814</v>
+        <v>0.96266</v>
       </c>
       <c r="G28" t="n">
-        <v>0.10846</v>
+        <v>0.11053</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00755</v>
+        <v>0.00774</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09472</v>
+        <v>0.09214</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12723</v>
+        <v>0.12598</v>
       </c>
     </row>
     <row r="29">
@@ -1179,28 +1083,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74152</v>
+        <v>0.75706</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08229</v>
+        <v>0.08046</v>
       </c>
       <c r="E29" t="n">
-        <v>0.59973</v>
+        <v>0.59951</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95518</v>
+        <v>0.93787</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1116</v>
+        <v>0.10805</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00757</v>
+        <v>0.00753</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09464</v>
+        <v>0.09242</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12624</v>
+        <v>0.12679</v>
       </c>
     </row>
     <row r="30">
@@ -1210,28 +1114,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.76448</v>
+        <v>0.74503</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08087999999999999</v>
+        <v>0.08185000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.61112</v>
+        <v>0.60895</v>
       </c>
       <c r="F30" t="n">
-        <v>0.94503</v>
+        <v>0.9384</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10764</v>
+        <v>0.11039</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0077</v>
+        <v>0.00756</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09544999999999999</v>
+        <v>0.09239</v>
       </c>
       <c r="J30" t="n">
-        <v>0.12612</v>
+        <v>0.12578</v>
       </c>
     </row>
   </sheetData>
